--- a/miranda_sales_analysis.results.Q3.xlsx
+++ b/miranda_sales_analysis.results.Q3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nataliamiranda\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0D7B41B-CF43-45CF-84E0-6931F94AA951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF78E8FA-D824-44A0-A315-6201A0FE5C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{99584759-4D64-432A-861D-E1F2FEAA7BF0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{99584759-4D64-432A-861D-E1F2FEAA7BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -528,13 +528,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -612,6 +611,36 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>TERRITORY</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> VS REGION</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1683,7 +1712,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C7E0AFD-A381-40E9-B891-9B24D9A7D79F}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C7E0AFD-A381-40E9-B891-9B24D9A7D79F}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -2092,7 +2121,7 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>2392222.44</v>
       </c>
     </row>
@@ -2100,7 +2129,7 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>6723039.5300000003</v>
       </c>
     </row>
@@ -2108,7 +2137,7 @@
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>9115261.9700000007</v>
       </c>
     </row>
